--- a/artfynd/A 45895-2025 artfynd.xlsx
+++ b/artfynd/A 45895-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136347695</v>
       </c>
       <c r="B3" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136347696</v>
       </c>
       <c r="B4" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>136347668</v>
       </c>
       <c r="B5" t="n">
-        <v>98210</v>
+        <v>98213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 45895-2025 artfynd.xlsx
+++ b/artfynd/A 45895-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136347695</v>
       </c>
       <c r="B3" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136347696</v>
       </c>
       <c r="B4" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>136347668</v>
       </c>
       <c r="B5" t="n">
-        <v>98213</v>
+        <v>98214</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 45895-2025 artfynd.xlsx
+++ b/artfynd/A 45895-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136347695</v>
       </c>
       <c r="B3" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136347696</v>
       </c>
       <c r="B4" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>136347668</v>
       </c>
       <c r="B5" t="n">
-        <v>98214</v>
+        <v>98219</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 45895-2025 artfynd.xlsx
+++ b/artfynd/A 45895-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136347695</v>
       </c>
       <c r="B3" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136347696</v>
       </c>
       <c r="B4" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>136347668</v>
       </c>
       <c r="B5" t="n">
-        <v>98219</v>
+        <v>98221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 45895-2025 artfynd.xlsx
+++ b/artfynd/A 45895-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136347695</v>
       </c>
       <c r="B3" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136347696</v>
       </c>
       <c r="B4" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>136347668</v>
       </c>
       <c r="B5" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 45895-2025 artfynd.xlsx
+++ b/artfynd/A 45895-2025 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>136347695</v>
       </c>
       <c r="B3" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136347696</v>
       </c>
       <c r="B4" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         <v>136347668</v>
       </c>
       <c r="B5" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
